--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486973_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486973_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4363</v>
+        <v>3.3169</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3922</v>
+        <v>3.6286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0441</v>
+        <v>-0.3116</v>
       </c>
       <c r="G2" t="n">
         <v>4.6476</v>
@@ -610,13 +610,13 @@
         <v>3.4908</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3025</v>
+        <v>-1.4218</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0076</v>
+        <v>-0.7712</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2949</v>
+        <v>-0.6506</v>
       </c>
       <c r="V2" t="n">
         <v>0.7072000000000001</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7011</v>
+        <v>2.9309</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6519</v>
+        <v>3.8224</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9508</v>
+        <v>-0.8915</v>
       </c>
       <c r="G3" t="n">
         <v>2.0498</v>
@@ -688,13 +688,13 @@
         <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2584</v>
+        <v>-1.0286</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5774</v>
+        <v>-0.4069</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.681</v>
+        <v>-0.6217</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3491</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6738</v>
+        <v>2.6713</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1331</v>
+        <v>2.1602</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5111</v>
       </c>
       <c r="G4" t="n">
         <v>3.2874</v>
@@ -766,13 +766,13 @@
         <v>3.2855</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2518</v>
+        <v>-1.2543</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7441</v>
+        <v>-0.717</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5077</v>
+        <v>-0.5374</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5938</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. TRAORE</t>
+          <t>A. LLORCA CASTILLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9258</v>
+        <v>1.1462</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1061</v>
+        <v>-0.9157</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8197</v>
+        <v>2.062</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1359</v>
+        <v>0.1904</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6163</v>
+        <v>-0.1617</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7522</v>
+        <v>0.3521</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8076</v>
+        <v>-0.3344</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6103</v>
+        <v>-0.0574</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1973</v>
+        <v>-0.277</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9435</v>
+        <v>0.5248</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006</v>
+        <v>-0.1044</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9495</v>
+        <v>0.6291</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8481</v>
+        <v>3.2855</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8748</v>
+        <v>3.2855</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.673</v>
+        <v>-1.0286</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.5814</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.758</v>
+        <v>-0.4473</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1134</v>
+        <v>-1.301</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3536</v>
+        <v>-1.301</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8614000000000001</v>
+        <v>1.055</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0269</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8884</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.4573</v>
@@ -922,13 +922,13 @@
         <v>0.4107</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0066</v>
+        <v>0.1869</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0659</v>
+        <v>0.0387</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0593</v>
+        <v>0.1482</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LLORCA CASTILLO</t>
+          <t>B. TRAORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3795</v>
+        <v>0.5576</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5046</v>
+        <v>-0.351</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8841</v>
+        <v>0.9086</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1904</v>
+        <v>-0.1359</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1617</v>
+        <v>0.6163</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3521</v>
+        <v>-0.7522</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3344</v>
+        <v>0.8076</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0574</v>
+        <v>0.6103</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.277</v>
+        <v>0.1973</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5248</v>
+        <v>-0.9435</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1044</v>
+        <v>0.006</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6291</v>
+        <v>-0.9495</v>
       </c>
       <c r="P7" t="n">
-        <v>3.2855</v>
+        <v>1.8481</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>3.2855</v>
+        <v>2.8748</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7954</v>
+        <v>-1.0412</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1702</v>
+        <v>-0.3722</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6251</v>
+        <v>-0.6691</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.301</v>
+        <v>-0.1134</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.301</v>
+        <v>-0.3536</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1274</v>
+        <v>-0.9932</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0731</v>
+        <v>-0.9685</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0543</v>
+        <v>-0.0246</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4304</v>
@@ -1078,13 +1078,13 @@
         <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0461</v>
+        <v>0.0881</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0659</v>
+        <v>0.0387</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2402</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. CUELLAR GARCIA</t>
+          <t>P. RENANE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5778</v>
+        <v>-1.8077</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2306</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3471</v>
+        <v>-0.9786</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2917</v>
+        <v>-1.3234</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8629</v>
+        <v>-0.6974</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4288</v>
+        <v>-0.6261</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0679</v>
+        <v>-0.6974</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6161</v>
+        <v>-0.6974</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3596</v>
+        <v>-0.6261</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2468</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1127</v>
+        <v>-0.6261</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5381</v>
+        <v>-0.6896</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4879</v>
+        <v>-0.1317</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0502</v>
+        <v>-0.5579</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6456</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8858</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. RENANE</t>
+          <t>D. CUELLAR GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8736</v>
+        <v>-2.3997</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.895</v>
+        <v>-0.7265</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9786</v>
+        <v>-1.6732</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3234</v>
+        <v>-1.2917</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6974</v>
+        <v>-0.8629</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6261</v>
+        <v>-0.4288</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6974</v>
+        <v>0.0679</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6974</v>
+        <v>-0.6161</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6261</v>
+        <v>-1.3596</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.2468</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6261</v>
+        <v>-1.1127</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2053</v>
+        <v>1.8481</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.2838</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1976</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5579</v>
+        <v>-0.2759</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.6456</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.8858</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7457</v>
+        <v>-4.4319</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9254</v>
+        <v>-1.6116</v>
       </c>
       <c r="F11" t="n">
         <v>-2.8203</v>
@@ -1312,10 +1312,10 @@
         <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6896</v>
+        <v>-0.3758</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3216</v>
+        <v>-0.0078</v>
       </c>
       <c r="U11" t="n">
         <v>-0.368</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1701</v>
+        <v>-4.9033</v>
       </c>
       <c r="E12" t="n">
         <v>-4.5098</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6603</v>
+        <v>-0.3935</v>
       </c>
       <c r="G12" t="n">
         <v>1.0185</v>
@@ -1390,13 +1390,13 @@
         <v>1.4374</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3022</v>
+        <v>-1.0355</v>
       </c>
       <c r="T12" t="n">
         <v>-0.3566</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9456</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2169</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.516700000000001</v>
+        <v>-2.857899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8820999999999994</v>
+        <v>-0.2232999999999992</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6343</v>
+        <v>-2.634300000000001</v>
       </c>
       <c r="G13" t="n">
         <v>5.958399999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>6.537</v>
+        <v>6.536999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5786</v>
+        <v>-0.5785999999999998</v>
       </c>
       <c r="J13" t="n">
         <v>12.818</v>
@@ -1447,7 +1447,7 @@
         <v>6.9134</v>
       </c>
       <c r="L13" t="n">
-        <v>5.904699999999999</v>
+        <v>5.9047</v>
       </c>
       <c r="M13" t="n">
         <v>-6.8595</v>
@@ -1459,7 +1459,7 @@
         <v>-6.483200000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>7.187199999999999</v>
+        <v>7.187200000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.3471</v>
@@ -1468,13 +1468,13 @@
         <v>20.5343</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.542999999999999</v>
+        <v>-7.8842</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.934</v>
+        <v>-3.275299999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.6089</v>
+        <v>-4.6092</v>
       </c>
       <c r="V13" t="n">
         <v>-8.1191</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0511</v>
+        <v>7.1331</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4033</v>
+        <v>4.8803</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6478</v>
+        <v>2.2528</v>
       </c>
       <c r="G14" t="n">
         <v>1.9818</v>
@@ -1546,13 +1546,13 @@
         <v>2.0534</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5539</v>
+        <v>1.6359</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8517</v>
+        <v>1.3287</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2978</v>
+        <v>0.3072</v>
       </c>
       <c r="V14" t="n">
         <v>2.4886</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1433</v>
+        <v>2.6752</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2592</v>
+        <v>3.4223</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1159</v>
+        <v>-0.7471</v>
       </c>
       <c r="G15" t="n">
         <v>0.4443</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0624</v>
+        <v>1.5943</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5728</v>
+        <v>0.736</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4896</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>1.0472</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>E. ORTIZ TORRES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4984</v>
+        <v>2.0085</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6947</v>
+        <v>-0.6916</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1963</v>
+        <v>2.7002</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0043</v>
+        <v>2.9142</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5966</v>
+        <v>-0.3117</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4077</v>
+        <v>3.2258</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4364</v>
+        <v>1.9663</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5153</v>
+        <v>0.0195</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0789</v>
+        <v>1.9469</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5679</v>
+        <v>0.9479</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0813</v>
+        <v>-0.3311</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4866</v>
+        <v>1.279</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4107</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R16" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3241</v>
+        <v>0.7371</v>
       </c>
       <c r="T16" t="n">
-        <v>2.739</v>
+        <v>0.4222</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5851</v>
+        <v>0.3149</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ORTIZ TORRES</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6755</v>
+        <v>1.5108</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7962</v>
+        <v>1.5208</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4718</v>
+        <v>-0.01</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9142</v>
+        <v>-3.8388</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3117</v>
+        <v>-1.5414</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2258</v>
+        <v>-2.2974</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9663</v>
+        <v>-0.8592</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0195</v>
+        <v>-0.4638</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9469</v>
+        <v>-0.3954</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9479</v>
+        <v>-2.9797</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3311</v>
+        <v>-1.0777</v>
       </c>
       <c r="O17" t="n">
-        <v>1.279</v>
+        <v>-1.902</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4041</v>
+        <v>1.4461</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3176</v>
+        <v>0.612</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.4661</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.7679</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1248</v>
+        <v>0.9643</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2655</v>
+        <v>1.0211</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1407</v>
+        <v>-0.0568</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.8388</v>
+        <v>-1.0043</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5414</v>
+        <v>-0.5966</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2974</v>
+        <v>-0.4077</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8592</v>
+        <v>-0.4364</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4638</v>
+        <v>-0.5153</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3954</v>
+        <v>0.0789</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9797</v>
+        <v>-0.5679</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0777</v>
+        <v>-0.0813</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.902</v>
+        <v>-0.4866</v>
       </c>
       <c r="P18" t="n">
-        <v>1.4374</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0602</v>
+        <v>1.7899</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6433</v>
+        <v>1.0653</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7034</v>
+        <v>0.7246</v>
       </c>
       <c r="V18" t="n">
-        <v>2.4661</v>
+        <v>0.5893</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7679</v>
+        <v>1.4189</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6982</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PARRA BAEZ</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5675</v>
+        <v>-0.4731</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8015</v>
+        <v>-2.2535</v>
       </c>
       <c r="F19" t="n">
-        <v>0.234</v>
+        <v>1.7804</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4227</v>
+        <v>-1.6083</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.8538</v>
+        <v>-1.4952</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4311</v>
+        <v>-0.113</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4175</v>
+        <v>-2.0481</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.3577</v>
+        <v>-1.4691</v>
       </c>
       <c r="L19" t="n">
-        <v>2.7753</v>
+        <v>-0.579</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8402</v>
+        <v>0.4398</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4961</v>
+        <v>-0.0261</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3441</v>
+        <v>0.4659</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0534</v>
+        <v>1.0267</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.1068</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0534</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3111</v>
+        <v>0.1085</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2903</v>
+        <v>-0.2054</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0208</v>
+        <v>0.3139</v>
       </c>
       <c r="V19" t="n">
-        <v>2.5975</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5975</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ALVAREZ PUERTAS</t>
+          <t>J. PARRA BAEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0728</v>
+        <v>-0.7105</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5423</v>
+        <v>-0.9061</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4694</v>
+        <v>0.1956</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8093</v>
+        <v>-2.4227</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5222</v>
+        <v>-3.8538</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3315</v>
+        <v>1.4311</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7518</v>
+        <v>0.4175</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6034</v>
+        <v>-2.3577</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3552</v>
+        <v>2.7753</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0575</v>
+        <v>-2.8402</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0813</v>
+        <v>-1.4961</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0238</v>
+        <v>-1.3441</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4107</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>-4.1068</v>
       </c>
       <c r="R20" t="n">
-        <v>0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1472</v>
+        <v>1.1681</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2362</v>
+        <v>0.1857</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0891</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2.5975</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.5975</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1426</v>
+        <v>-0.8149</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5674</v>
+        <v>0.7197</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4247</v>
+        <v>-1.5346</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6083</v>
+        <v>0.2754</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4952</v>
+        <v>0.4965</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.113</v>
+        <v>-0.2211</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0481</v>
+        <v>2.7186</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4691</v>
+        <v>1.548</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.579</v>
+        <v>1.1706</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4398</v>
+        <v>-2.4432</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0261</v>
+        <v>-1.0516</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4659</v>
+        <v>-1.3917</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0267</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5611</v>
+        <v>0.649</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5192</v>
+        <v>0.2517</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0418</v>
+        <v>0.3973</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1088</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.8295</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.7207</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>M. ALVAREZ PUERTAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0876</v>
+        <v>-1.282</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1171</v>
+        <v>-1.7515</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9705</v>
+        <v>0.4694</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2754</v>
+        <v>-0.8093</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4965</v>
+        <v>0.5222</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2211</v>
+        <v>-1.3315</v>
       </c>
       <c r="J22" t="n">
-        <v>2.7186</v>
+        <v>-0.7518</v>
       </c>
       <c r="K22" t="n">
-        <v>1.548</v>
+        <v>0.6034</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1706</v>
+        <v>-1.3552</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4432</v>
+        <v>-0.0575</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0516</v>
+        <v>-0.0813</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3917</v>
+        <v>0.0238</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.8481</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6238</v>
+        <v>-0.062</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5851</v>
+        <v>0.027</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0386</v>
+        <v>-0.0891</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1088</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8295</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.1061</v>
+        <v>-6.1002</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1639</v>
+        <v>-3.3271</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9422</v>
+        <v>-2.7731</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8908</v>
@@ -2248,13 +2248,13 @@
         <v>1.2321</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1352</v>
+        <v>0.8708</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.651</v>
+        <v>0.1858</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5158</v>
+        <v>0.6849</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1786</v>
@@ -2281,37 +2281,37 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.516500000000001</v>
+        <v>4.9112</v>
       </c>
       <c r="E24" t="n">
-        <v>2.634300000000001</v>
+        <v>2.6344</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8821000000000003</v>
+        <v>2.2768</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.958499999999999</v>
+        <v>-5.958500000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-6.536899999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5786</v>
+        <v>0.5785999999999996</v>
       </c>
       <c r="J24" t="n">
         <v>6.8595</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3764000000000003</v>
+        <v>0.3764000000000006</v>
       </c>
       <c r="L24" t="n">
-        <v>6.483200000000002</v>
+        <v>6.4832</v>
       </c>
       <c r="M24" t="n">
         <v>-12.818</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.913600000000001</v>
+        <v>-6.913599999999999</v>
       </c>
       <c r="O24" t="n">
         <v>-5.9046</v>
@@ -2326,16 +2326,16 @@
         <v>13.3472</v>
       </c>
       <c r="S24" t="n">
-        <v>8.542900000000001</v>
+        <v>9.9377</v>
       </c>
       <c r="T24" t="n">
-        <v>4.609</v>
+        <v>4.609000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>3.9339</v>
+        <v>5.3287</v>
       </c>
       <c r="V24" t="n">
-        <v>8.118900000000002</v>
+        <v>8.1189</v>
       </c>
       <c r="W24" t="n">
         <v>11.7</v>
